--- a/data/Long-Chinesisch_Lektionen.xlsx
+++ b/data/Long-Chinesisch_Lektionen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rruhe\Downloads\HSK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F599DCD-8D11-402D-8711-66BFFA57B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2A6CA3-ABA3-4084-A25F-DA76925B8D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51540" yWindow="-6090" windowWidth="49905" windowHeight="24195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30938,7 +30938,6 @@
       <c r="I778" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I700" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I419">
     <sortCondition ref="H48:H76"/>
   </sortState>
